--- a/labs/extinction/lab-extinction.xlsx
+++ b/labs/extinction/lab-extinction.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Exercise I" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Exercise II" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Exercise I" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Exercise II" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
   <si>
     <t xml:space="preserve">PART A - no stochasticity</t>
   </si>
@@ -333,13 +333,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P67"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.56"/>
@@ -451,7 +557,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
@@ -476,7 +582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
@@ -495,7 +601,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
@@ -511,7 +617,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>4</v>
       </c>
@@ -527,7 +633,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
@@ -543,7 +649,7 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
@@ -559,7 +665,7 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>7</v>
       </c>
@@ -575,7 +681,7 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>8</v>
       </c>
@@ -591,7 +697,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>9</v>
       </c>
@@ -607,7 +713,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>10</v>
       </c>
@@ -623,7 +729,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>11</v>
       </c>
@@ -639,7 +745,7 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>12</v>
       </c>
@@ -655,7 +761,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>13</v>
       </c>
@@ -671,7 +777,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>14</v>
       </c>
@@ -687,7 +793,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>15</v>
       </c>
@@ -703,7 +809,7 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>16</v>
       </c>
@@ -719,7 +825,7 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>17</v>
       </c>
@@ -735,7 +841,7 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>18</v>
       </c>
@@ -751,7 +857,7 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>19</v>
       </c>
@@ -767,7 +873,7 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
@@ -783,7 +889,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>21</v>
       </c>
@@ -799,7 +905,7 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>22</v>
       </c>
@@ -815,7 +921,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>23</v>
       </c>
@@ -831,7 +937,7 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>24</v>
       </c>
@@ -847,7 +953,7 @@
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
@@ -863,7 +969,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>26</v>
       </c>
@@ -879,7 +985,7 @@
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>27</v>
       </c>
@@ -895,7 +1001,7 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>28</v>
       </c>
@@ -911,7 +1017,7 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>29</v>
       </c>
@@ -927,7 +1033,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>30</v>
       </c>
@@ -943,8 +1049,7 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -995,7 +1100,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>1</v>
       </c>
@@ -1010,7 +1115,7 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>2</v>
       </c>
@@ -1025,7 +1130,7 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>3</v>
       </c>
@@ -1040,7 +1145,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>4</v>
       </c>
@@ -1055,7 +1160,7 @@
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>5</v>
       </c>
@@ -1070,7 +1175,7 @@
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
         <v>6</v>
       </c>
@@ -1085,7 +1190,7 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
         <v>7</v>
       </c>
@@ -1100,7 +1205,7 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
         <v>8</v>
       </c>
@@ -1115,7 +1220,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
         <v>9</v>
       </c>
@@ -1130,7 +1235,7 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
         <v>10</v>
       </c>
@@ -1145,7 +1250,7 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
         <v>11</v>
       </c>
@@ -1160,7 +1265,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
         <v>12</v>
       </c>
@@ -1175,7 +1280,7 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
         <v>13</v>
       </c>
@@ -1190,7 +1295,7 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
         <v>14</v>
       </c>
@@ -1205,7 +1310,7 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
         <v>15</v>
       </c>
@@ -1220,7 +1325,7 @@
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="n">
         <v>16</v>
       </c>
@@ -1235,7 +1340,7 @@
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="n">
         <v>17</v>
       </c>
@@ -1250,7 +1355,7 @@
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
         <v>18</v>
       </c>
@@ -1265,7 +1370,7 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
         <v>19</v>
       </c>
@@ -1280,7 +1385,7 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="n">
         <v>20</v>
       </c>
@@ -1295,7 +1400,7 @@
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="n">
         <v>21</v>
       </c>
@@ -1310,7 +1415,7 @@
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="n">
         <v>22</v>
       </c>
@@ -1325,7 +1430,7 @@
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="n">
         <v>23</v>
       </c>
@@ -1340,7 +1445,7 @@
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="n">
         <v>24</v>
       </c>
@@ -1355,7 +1460,7 @@
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="n">
         <v>25</v>
       </c>
@@ -1370,7 +1475,7 @@
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
         <v>26</v>
       </c>
@@ -1385,7 +1490,7 @@
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="n">
         <v>27</v>
       </c>
@@ -1400,7 +1505,7 @@
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="n">
         <v>28</v>
       </c>
@@ -1415,7 +1520,7 @@
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="n">
         <v>29</v>
       </c>
@@ -1430,7 +1535,7 @@
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
         <v>30</v>
       </c>
@@ -1464,8 +1569,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:N1048576"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.76"/>
@@ -1532,7 +1637,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D4" s="1" t="n">
         <v>1</v>
       </c>
@@ -1542,7 +1647,7 @@
       </c>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="n">
         <v>2</v>
       </c>
@@ -1552,7 +1657,7 @@
       </c>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="n">
         <v>3</v>
       </c>
@@ -1562,7 +1667,7 @@
       </c>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="n">
         <v>4</v>
       </c>
@@ -1572,7 +1677,7 @@
       </c>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="1" t="n">
         <v>5</v>
       </c>
@@ -1605,7 +1710,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>1</v>
       </c>
@@ -1620,7 +1725,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>2</v>
       </c>
@@ -1635,7 +1740,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>3</v>
       </c>
@@ -1650,7 +1755,7 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>4</v>
       </c>
@@ -1665,7 +1770,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>5</v>
       </c>
@@ -1697,7 +1802,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="n">
         <v>1</v>
       </c>
@@ -1708,7 +1813,7 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="1" t="n">
         <v>2</v>
       </c>
@@ -1719,7 +1824,7 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="1" t="n">
         <v>3</v>
       </c>
@@ -1730,7 +1835,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="1" t="n">
         <v>4</v>
       </c>
@@ -1741,7 +1846,7 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="1" t="n">
         <v>5</v>
       </c>
@@ -1752,7 +1857,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
@@ -1769,7 +1874,7 @@
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>39</v>
       </c>
@@ -1786,26 +1891,10 @@
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="1"/>
-    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="1"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
